--- a/assets/field-work-example.xlsx
+++ b/assets/field-work-example.xlsx
@@ -481,16 +481,16 @@
     <col width="48" customWidth="1" min="15" max="15"/>
     <col width="52" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
     <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
     <col width="18" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>실장결재여부(수리)</t>
+          <t>안전보건관리책임자결재여부(수리)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>실장결재여부</t>
+          <t>안전보건관리책임자결재여부</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>부장결재여부</t>
+          <t>팀장결재여부</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
